--- a/output/pdf_financials_xlsx/PGC.xlsx
+++ b/output/pdf_financials_xlsx/PGC.xlsx
@@ -5982,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>-0.015835</v>
       </c>
     </row>
     <row r="92">
@@ -9953,7 +9953,11 @@
           <t>Cumulative translation reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PGC.xlsx
+++ b/output/pdf_financials_xlsx/PGC.xlsx
@@ -1041,37 +1041,37 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00804</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000244</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000811</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002732</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.001378</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002461</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002074</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.002163</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002417</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.002771</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.004755</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -2019,37 +2019,37 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.652226</v>
+        <v>-0.660266</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.7080070000000001</v>
+        <v>-0.708251</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.731755</v>
+        <v>-0.7325660000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.692294</v>
+        <v>-0.695026</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.978857</v>
+        <v>-3.980235</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.7437049999999999</v>
+        <v>-0.746166</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.495569</v>
+        <v>-0.497643</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.711946</v>
+        <v>-1.714109</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.27478</v>
+        <v>-0.277197</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.319546</v>
+        <v>-0.322317</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.060278</v>
+        <v>0.055523</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.27018</v>
@@ -2135,37 +2135,37 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.652226</v>
+        <v>-0.660266</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.7080070000000001</v>
+        <v>-0.708251</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.731755</v>
+        <v>-0.7325660000000001</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.692294</v>
+        <v>-0.695026</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.978857</v>
+        <v>-3.980235</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.7437049999999999</v>
+        <v>-0.746166</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.495569</v>
+        <v>-0.497643</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.711946</v>
+        <v>-1.714109</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.27478</v>
+        <v>-0.277197</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.319546</v>
+        <v>-0.322317</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.060278</v>
+        <v>0.055523</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.27018</v>
@@ -2442,55 +2442,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.052967</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.082015</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.082015</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.058337</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.382065</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.00567</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003678</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.006749</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.002811</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.036667</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.011674</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.093667</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.112731</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.078774</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.014308</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.024216</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.014648</v>
       </c>
     </row>
     <row r="35">
@@ -2558,55 +2558,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.052967</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.082015</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.082015</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.058337</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.382065</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.00567</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003678</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.006749</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.002811</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.036667</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.011674</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.093667</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.112731</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.078774</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.014308</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.024216</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.014648</v>
       </c>
     </row>
     <row r="37">
@@ -3254,55 +3254,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.057742</v>
+        <v>0.004775</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.092015</v>
+        <v>0.01</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.092015</v>
+        <v>0.01</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.09375</v>
+        <v>0.035413</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.577614</v>
+        <v>0.195549</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.078455</v>
+        <v>0.072785</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.051372</v>
+        <v>0.047694</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.053769</v>
+        <v>0.04702</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.13048</v>
+        <v>0.127669</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.18453</v>
+        <v>0.147863</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.228797</v>
+        <v>0.217123</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.189327</v>
+        <v>0.09566</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.129529</v>
+        <v>0.016798</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.0968</v>
+        <v>0.018026</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.033524</v>
+        <v>0.019216</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.039048</v>
+        <v>0.014832</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.026986</v>
+        <v>0.012338</v>
       </c>
     </row>
     <row r="49">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -35738,7 +35738,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -40215,7 +40215,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -41920,7 +41920,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E343" s="5" t="n">

--- a/output/pdf_financials_xlsx/PGC.xlsx
+++ b/output/pdf_financials_xlsx/PGC.xlsx
@@ -777,25 +777,25 @@
         <v>0.1545</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.027968</v>
+        <v>0.133868</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.019385</v>
+        <v>0.020085</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.01539</v>
+        <v>0.01629</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.02164</v>
+        <v>0.02244</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.01534</v>
+        <v>0.01614</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.039755</v>
+        <v>0.043105</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.061703</v>
+        <v>0.06260300000000001</v>
       </c>
     </row>
     <row r="8">
@@ -951,10 +951,10 @@
         <v>0.2505</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.123968</v>
+        <v>0.229868</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.019485</v>
+        <v>0.020185</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.398477</v>
@@ -1013,10 +1013,10 @@
         <v>-0.2505</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.123968</v>
+        <v>-0.229868</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.019485</v>
+        <v>-0.020185</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-0.398477</v>
@@ -1337,13 +1337,13 @@
         <v>0.7080070000000001</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.67583</v>
+        <v>-0.231127</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.134017</v>
+        <v>-0.134017</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.243487</v>
+        <v>-0.243487</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -2291,7 +2291,7 @@
         <v>-100</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-92.35741470847483</v>
+        <v>-31.585298358057</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-19.35839397712533</v>
@@ -7040,10 +7040,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.009648</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.013392</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -7327,10 +7327,10 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.008619999999999999</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.040701</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -23382,7 +23382,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -23683,7 +23687,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -24566,7 +24574,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -26510,7 +26522,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -27997,7 +28013,11 @@
           <t>Deferred future income tax recovery</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -28797,7 +28817,11 @@
           <t>Future income tax recoveries</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E208" s="5" t="n">
         <v>-0.375662</v>
       </c>
@@ -29981,7 +30005,11 @@
           <t>Consulting and director fees</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -39407,7 +39435,11 @@
           <t>Deferred Income Tax Recovery (note 12)</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -40908,7 +40940,11 @@
           <t>Deferred Income Tax Recovery (note 14)</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
